--- a/Excel/ChapterData.xlsx
+++ b/Excel/ChapterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitWork\ETSource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{52B00356-2FFB-4FBF-9246-2C42370E2CDB}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{28476453-9A36-49DB-BA1C-796911C9CD3A}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="13230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -71,33 +71,6 @@
   </si>
   <si>
     <t>关卡</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Po</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ltID</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Arr</t>
-    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -151,6 +124,10 @@
   </si>
   <si>
     <t>long[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlotIDArr</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -568,7 +545,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>16</v>
@@ -585,10 +562,10 @@
         <v>5</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="3:7" x14ac:dyDescent="0.3">
@@ -602,10 +579,10 @@
         <v>7</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="6" spans="3:7" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -622,7 +599,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="3:7" x14ac:dyDescent="0.3">
@@ -639,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="3:7" x14ac:dyDescent="0.3">
@@ -656,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="3:7" x14ac:dyDescent="0.3">
@@ -673,7 +650,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ChapterData.xlsx
+++ b/Excel/ChapterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitWork\ETSource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{28476453-9A36-49DB-BA1C-796911C9CD3A}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{BAE7A0AE-8B34-4314-829D-B839B08AC272}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="13230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="29">
   <si>
     <t>id</t>
   </si>
@@ -38,9 +38,6 @@
   </si>
   <si>
     <t>Desc</t>
-  </si>
-  <si>
-    <t>long</t>
   </si>
   <si>
     <t>string</t>
@@ -128,6 +125,26 @@
   </si>
   <si>
     <t>PlotIDArr</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>long</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>难度</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HardLv</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>第5章</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>第6章</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -147,6 +164,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -154,11 +172,13 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -522,19 +542,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:G9"/>
+  <dimension ref="C3:H17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" style="2" customWidth="1"/>
     <col min="2" max="2" width="3.875" style="2" customWidth="1"/>
     <col min="3" max="3" width="5" style="2" customWidth="1"/>
     <col min="4" max="4" width="15.125" style="2" customWidth="1"/>
-    <col min="5" max="6" width="9.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="5" max="5" width="9.625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="15" style="2" customWidth="1"/>
+    <col min="8" max="8" width="30" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -545,13 +566,16 @@
         <v>2</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="3:7" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
@@ -562,95 +586,273 @@
         <v>5</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="3:7" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="6" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F6" s="1">
         <v>0</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="F7" s="1">
         <v>0</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="F8" s="6">
         <v>0</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="G8" s="1">
+        <v>3</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>19</v>
+      <c r="G9" s="1">
+        <v>4</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C10" s="1">
+        <v>5</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>5</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C11" s="1">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>6</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C12" s="1">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>7</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>8</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C14" s="1">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>9</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>10</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="6">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>11</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>12</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ChapterData.xlsx
+++ b/Excel/ChapterData.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20325"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitWork\ETSource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{BAE7A0AE-8B34-4314-829D-B839B08AC272}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{6F40785D-CE4E-44A9-A3B3-91DA6D8C57C9}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="13230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="54">
   <si>
     <t>id</t>
   </si>
@@ -43,55 +43,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>第一章</t>
-  </si>
-  <si>
-    <t>米克尔</t>
-  </si>
-  <si>
-    <t>第二章</t>
-  </si>
-  <si>
-    <t>纳洛</t>
-  </si>
-  <si>
-    <t>第三章</t>
-  </si>
-  <si>
-    <t>麦德罗</t>
-  </si>
-  <si>
-    <t>第四章</t>
-  </si>
-  <si>
-    <t>蒂娜</t>
-  </si>
-  <si>
     <t>关卡</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>,2</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2,3</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -140,11 +92,136 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>第5章</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>第6章</t>
+    <t>初学乍练</t>
+  </si>
+  <si>
+    <t>初窥门径</t>
+  </si>
+  <si>
+    <t>略知一二</t>
+  </si>
+  <si>
+    <t>粗懂皮毛</t>
+  </si>
+  <si>
+    <t>半生不熟</t>
+  </si>
+  <si>
+    <t>登堂入室</t>
+  </si>
+  <si>
+    <t>略有小成</t>
+  </si>
+  <si>
+    <t>鹤立鸡群</t>
+  </si>
+  <si>
+    <t>青出于蓝</t>
+  </si>
+  <si>
+    <t>融会贯通</t>
+  </si>
+  <si>
+    <t>心领神会</t>
+  </si>
+  <si>
+    <t>炉火纯青</t>
+  </si>
+  <si>
+    <t>略有大成</t>
+  </si>
+  <si>
+    <t>豁然贯通</t>
+  </si>
+  <si>
+    <t>出类拔萃</t>
+  </si>
+  <si>
+    <t>罕有敌手</t>
+  </si>
+  <si>
+    <t>技冠群雄</t>
+  </si>
+  <si>
+    <t>神乎其技</t>
+  </si>
+  <si>
+    <t>出神入化</t>
+  </si>
+  <si>
+    <t>9,10,11,12,13,14,15,16,17,18,19,20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>57,58,59,60,61,62,63,64,65,66,67,68,69,70,71,72,73,74,75,76,77,78,79,80</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,101,102,103,104,105,106,107,108,81,82,83,84,85,86,87,88,89,90,91,92,93,94,95,96,97,98,99</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>109,110,111,112,113,114,115,116,117,118,119,120,121,122,123,124,125,126,127,128,129,130,131,132,133,134,135,136,137,138,139,140</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>141,142,143,144,145,146,147,148,149,150,151,152,153,154,155,156,157,158,159,160,161,162,163,164,165,166,167,168,169,170,171,172,173,174,175,176</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>177,178,179,180,181,182,183,184,185,186,187,188,189,190,191,192,193,194,195,196,197,198,199,200,201,202,203,204,205,206,207,208,209,210,211,212,213,214,215,216</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>217,218,219,220,221,222,223,224,225,226,227,228,229,230,231,232,233,234,235,236,237,238,239,240,241,242,243,244,245,246,247,248,249,250,251,252,253,254,255,256,257,258,259,260</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>261,262,263,264,265,266,267,268,269,270,271,272,273,274,275,276,277,278,279,280,281,282,283,284,285,286,287,288,289,290,291,292,293,294,295,296,297,298,299,300,301,302,303,304,305,306,307,308</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>309,310,311,312,313,314,315,316,317,318,319,320,321,322,323,324,325,326,327,328,329,330,331,332,333,334,335,336,337,338,339,340,341,342,343,344,345,346,347,348,349,350,351,352,353,354,355,356,357,358,359,360</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>361,362,363,364,365,366,367,368,369,370,371,372,373,374,375,376,377,378,379,380,381,382,383,384,385,386,387,388,389,390,391,392,393,394,395,396,397,398,399,400,401,402,403,404,405,406,407,408,409,410,411,412,413,414,415,416</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>417,418,419,420,421,422,423,424,425,426,427,428,429,430,431,432,433,434,435,436,437,438,439,440,441,442,443,444,445,446,447,448,449,450,451,452,453,454,455,456,457,458,459,460,461,462,463,464,465,466,467,468,469,470,471,472,473,474,475,476</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>541,542,543,544,545,546,547,548,549,550,551,552,553,554,555,556,557,558,559,560,561,562,563,564,565,566,567,568,569,570,571,572,573,574,575,576,577,578,579,580,581,582,583,584,585,586,587,588,589,590,591,592,593,594,595,596,597,598,599,600,601,602,603,604,605,606,607,608</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>609,610,611,612,613,614,615,616,617,618,619,620,621,622,623,624,625,626,627,628,629,630,631,632,633,634,635,636,637,638,639,640,641,642,643,644,645,646,647,648,649,650,651,652,653,654,655,656,657,658,659,660,661,662,663,664,665,666,667,668,669,670,671,672,673,674,675,676,677,678,679,680</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>681,682,683,684,685,686,687,688,689,690,691,692,693,694,695,696,697,698,699,700,701,702,703,704,705,706,707,708,709,710,711,712,713,714,715,716,717,718,719,720,721,722,723,724,725,726,727,728,729,730,731,732,733,734,735,736,737,738,739,740,741,742,743,744,745,746,747,748,749,750,751,752,753,754,755,756</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>757,758,759,760,761,762,763,764,765,766,767,768,769,770,771,772,773,774,775,776,777,778,779,780,781,782,783,784,785,786,787,788,789,790,791,792,793,794,795,796,797,798,799,800,801,802,803,804,805,806,807,808,809,810,811,812,813,814,815,816,817,818,819,820,821,822,823,824,825,826,827,828,829,830,831,832,833,834,835,836</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6,7,8</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>477,478,479,480,481,482,483,484,485,486,487,488,489,490,491,492,493,494,495,496,497,498,499,500,501,502,503,504,505,506,507,508,509,510,511,512,513,514,515,516,517,518,519,520,521,522,523,524,525,526,527,528,529,530,531,532,533,534,535,536,537,538,539,540</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -152,7 +229,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,6 +274,18 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -224,7 +313,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -233,10 +322,20 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -542,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:H17"/>
+  <dimension ref="C3:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" style="2" customWidth="1"/>
@@ -551,7 +650,7 @@
     <col min="4" max="4" width="15.125" style="2" customWidth="1"/>
     <col min="5" max="5" width="9.625" style="2" customWidth="1"/>
     <col min="6" max="7" width="15" style="2" customWidth="1"/>
-    <col min="8" max="8" width="30" style="2" customWidth="1"/>
+    <col min="8" max="8" width="144.25" style="2" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -566,13 +665,13 @@
         <v>2</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="3:8" x14ac:dyDescent="0.3">
@@ -586,18 +685,18 @@
         <v>5</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>6</v>
@@ -606,24 +705,24 @@
         <v>6</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>8</v>
+      <c r="D6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -631,19 +730,19 @@
       <c r="G6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>16</v>
+      <c r="H6" s="10" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>10</v>
+      <c r="D7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -651,59 +750,59 @@
       <c r="G7" s="1">
         <v>2</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>17</v>
+      <c r="H7" s="7" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="6">
+      <c r="D8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="5">
         <v>0</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>18</v>
+      <c r="H8" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>14</v>
+      <c r="D9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="F9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>18</v>
+      <c r="H9" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>8</v>
+      <c r="D10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -711,99 +810,99 @@
       <c r="G10" s="1">
         <v>5</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>16</v>
+      <c r="H10" s="7" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="1">
+      <c r="D11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="5">
         <v>0</v>
       </c>
       <c r="G11" s="1">
         <v>6</v>
       </c>
-      <c r="H11" s="5" t="s">
-        <v>17</v>
+      <c r="H11" s="7" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="6">
+      <c r="D12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12" s="1">
         <v>7</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>18</v>
+      <c r="H12" s="8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C13" s="1">
         <v>8</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>14</v>
+      <c r="D13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="F13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
         <v>8</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>18</v>
+      <c r="H13" s="8" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C14" s="1">
         <v>9</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="1">
+      <c r="D14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="5">
         <v>0</v>
       </c>
       <c r="G14" s="1">
         <v>9</v>
       </c>
-      <c r="H14" s="5" t="s">
-        <v>16</v>
+      <c r="H14" s="8" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>10</v>
+      <c r="D15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -811,48 +910,188 @@
       <c r="G15" s="1">
         <v>10</v>
       </c>
-      <c r="H15" s="5" t="s">
-        <v>17</v>
+      <c r="H15" s="8" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C16" s="1">
         <v>11</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="6">
+      <c r="D16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1">
         <v>11</v>
       </c>
-      <c r="H16" s="5" t="s">
-        <v>18</v>
+      <c r="H16" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C17" s="1">
         <v>12</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="1">
-        <v>1</v>
+      <c r="D17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
       </c>
       <c r="G17" s="1">
         <v>12</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C18" s="1">
+        <v>13</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>13</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C19" s="1">
+        <v>14</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>14</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C20" s="1">
+        <v>15</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="5">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>15</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C21" s="1">
+        <v>16</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>16</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C22" s="1">
+        <v>17</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>17</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C23" s="1">
         <v>18</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" s="5">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>18</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>19</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ChapterData.xlsx
+++ b/Excel/ChapterData.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20325"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitWork\ETSource\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{6F40785D-CE4E-44A9-A3B3-91DA6D8C57C9}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="13230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28695" windowHeight="13050"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54">
   <si>
     <t>id</t>
   </si>
@@ -31,6 +25,15 @@
     <t>描述</t>
   </si>
   <si>
+    <t>解锁消耗</t>
+  </si>
+  <si>
+    <t>难度</t>
+  </si>
+  <si>
+    <t>关卡</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -40,18 +43,14 @@
     <t>Desc</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>关卡</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁消耗</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>C</t>
     </r>
     <r>
@@ -60,176 +59,155 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>hargeNum</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HardLv</t>
+  </si>
+  <si>
+    <t>PlotIDArr</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>string</t>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>long[]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>PlotIDArr</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>long</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>难度</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HardLv</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>初学乍练</t>
   </si>
   <si>
+    <t>254,257,249,259,303,282,304,290</t>
+  </si>
+  <si>
     <t>初窥门径</t>
   </si>
   <si>
+    <t>294,279,52,56,105,93,96,144,168,156,162,24</t>
+  </si>
+  <si>
     <t>略知一二</t>
   </si>
   <si>
+    <t>21,22,23,20,25,26,27,28,29,30,31,32,33,34,35,36</t>
+  </si>
+  <si>
     <t>粗懂皮毛</t>
   </si>
   <si>
+    <t>37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,11,53,54,55,12</t>
+  </si>
+  <si>
     <t>半生不熟</t>
   </si>
   <si>
+    <t>57,58,59,60,61,62,63,64,65,66,67,68,69,70,71,72,73,74,75,76,77,78,79,80</t>
+  </si>
+  <si>
     <t>登堂入室</t>
   </si>
   <si>
+    <t>100,101,102,103,104,13,106,107,108,81,82,83,84,85,86,87,88,89,90,91,92,14,94,95,15,97,98,99</t>
+  </si>
+  <si>
     <t>略有小成</t>
   </si>
   <si>
+    <t>109,110,111,112,113,114,115,116,117,118,119,120,121,122,123,124,125,126,127,128,129,130,131,132,133,134,135,136,137,138,139,140</t>
+  </si>
+  <si>
     <t>鹤立鸡群</t>
   </si>
   <si>
+    <t>141,142,143,16,145,146,147,148,149,150,151,152,153,154,155,18,157,158,159,160,161,19,163,164,165,166,167,17,169,170,171,172,173,174,175,176</t>
+  </si>
+  <si>
     <t>青出于蓝</t>
   </si>
   <si>
+    <t>177,178,179,180,181,182,183,184,185,186,187,188,189,190,191,192,193,194,195,196,197,198,199,200,201,202,203,204,205,206,207,208,209,210,211,212,213,214,215,216</t>
+  </si>
+  <si>
     <t>融会贯通</t>
   </si>
   <si>
+    <t>217,218,219,220,221,222,223,224,225,226,227,228,229,230,231,232,233,234,235,236,237,238,239,240,241,242,243,244,245,246,247,248,3,250,251,252,253,1,255,256,2,258,4,260</t>
+  </si>
+  <si>
     <t>心领神会</t>
   </si>
   <si>
+    <t>261,262,263,264,265,266,267,268,269,270,271,272,273,274,275,276,277,278,10,280,281,6,283,284,285,286,287,288,289,8,291,292,293,9,295,296,297,298,299,300,301,302,5,7,305,306,307,308</t>
+  </si>
+  <si>
     <t>炉火纯青</t>
   </si>
   <si>
+    <t>309,310,311,312,313,314,315,316,317,318,319,320,321,322,323,324,325,326,327,328,329,330,331,332,333,334,335,336,337,338,339,340,341,342,343,344,345,346,347,348,349,350,351,352,353,354,355,356,357,358,359,360</t>
+  </si>
+  <si>
     <t>略有大成</t>
   </si>
   <si>
+    <t>361,362,363,364,365,366,367,368,369,370,371,372,373,374,375,376,377,378,379,380,381,382,383,384,385,386,387,388,389,390,391,392,393,394,395,396,397,398,399,400,401,402,403,404,405,406,407,408,409,410,411,412,413,414,415,416</t>
+  </si>
+  <si>
     <t>豁然贯通</t>
   </si>
   <si>
+    <t>417,418,419,420,421,422,423,424,425,426,427,428,429,430,431,432,433,434,435,436,437,438,439,440,441,442,443,444,445,446,447,448,449,450,451,452,453,454,455,456,457,458,459,460,461,462,463,464,465,466,467,468,469,470,471,472,473,474,475,476</t>
+  </si>
+  <si>
     <t>出类拔萃</t>
   </si>
   <si>
+    <t>477,478,479,480,481,482,483,484,485,486,487,488,489,490,491,492,493,494,495,496,497,498,499,500,501,502,503,504,505,506,507,508,509,510,511,512,513,514,515,516,517,518,519,520,521,522,523,524,525,526,527,528,529,530,531,532,533,534,535,536,537,538,539,540</t>
+  </si>
+  <si>
     <t>罕有敌手</t>
   </si>
   <si>
+    <t>541,542,543,544,545,546,547,548,549,550,551,552,553,554,555,556,557,558,559,560,561,562,563,564,565,566,567,568,569,570,571,572,573,574,575,576,577,578,579,580,581,582,583,584,585,586,587,588,589,590,591,592,593,594,595,596,597,598,599,600,601,602,603,604,605,606,607,608</t>
+  </si>
+  <si>
     <t>技冠群雄</t>
   </si>
   <si>
+    <t>609,610,611,612,613,614,615,616,617,618,619,620,621,622,623,624,625,626,627,628,629,630,631,632,633,634,635,636,637,638,639,640,641,642,643,644,645,646,647,648,649,650,651,652,653,654,655,656,657,658,659,660,661,662,663,664,665,666,667,668,669,670,671,672,673,674,675,676,677,678,679,680</t>
+  </si>
+  <si>
     <t>神乎其技</t>
   </si>
   <si>
+    <t>681,682,683,684,685,686,687,688,689,690,691,692,693,694,695,696,697,698,699,700,701,702,703,704,705,706,707,708,709,710,711,712,713,714,715,716,717,718,719,720,721,722,723,724,725,726,727,728,729,730,731,732,733,734,735,736,737,738,739,740,741,742,743,744,745,746,747,748,749,750,751,752,753,754,755,756</t>
+  </si>
+  <si>
     <t>出神入化</t>
   </si>
   <si>
-    <t>9,10,11,12,13,14,15,16,17,18,19,20</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>57,58,59,60,61,62,63,64,65,66,67,68,69,70,71,72,73,74,75,76,77,78,79,80</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>100,101,102,103,104,105,106,107,108,81,82,83,84,85,86,87,88,89,90,91,92,93,94,95,96,97,98,99</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>109,110,111,112,113,114,115,116,117,118,119,120,121,122,123,124,125,126,127,128,129,130,131,132,133,134,135,136,137,138,139,140</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>141,142,143,144,145,146,147,148,149,150,151,152,153,154,155,156,157,158,159,160,161,162,163,164,165,166,167,168,169,170,171,172,173,174,175,176</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>177,178,179,180,181,182,183,184,185,186,187,188,189,190,191,192,193,194,195,196,197,198,199,200,201,202,203,204,205,206,207,208,209,210,211,212,213,214,215,216</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>217,218,219,220,221,222,223,224,225,226,227,228,229,230,231,232,233,234,235,236,237,238,239,240,241,242,243,244,245,246,247,248,249,250,251,252,253,254,255,256,257,258,259,260</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>261,262,263,264,265,266,267,268,269,270,271,272,273,274,275,276,277,278,279,280,281,282,283,284,285,286,287,288,289,290,291,292,293,294,295,296,297,298,299,300,301,302,303,304,305,306,307,308</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>309,310,311,312,313,314,315,316,317,318,319,320,321,322,323,324,325,326,327,328,329,330,331,332,333,334,335,336,337,338,339,340,341,342,343,344,345,346,347,348,349,350,351,352,353,354,355,356,357,358,359,360</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>361,362,363,364,365,366,367,368,369,370,371,372,373,374,375,376,377,378,379,380,381,382,383,384,385,386,387,388,389,390,391,392,393,394,395,396,397,398,399,400,401,402,403,404,405,406,407,408,409,410,411,412,413,414,415,416</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>417,418,419,420,421,422,423,424,425,426,427,428,429,430,431,432,433,434,435,436,437,438,439,440,441,442,443,444,445,446,447,448,449,450,451,452,453,454,455,456,457,458,459,460,461,462,463,464,465,466,467,468,469,470,471,472,473,474,475,476</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>541,542,543,544,545,546,547,548,549,550,551,552,553,554,555,556,557,558,559,560,561,562,563,564,565,566,567,568,569,570,571,572,573,574,575,576,577,578,579,580,581,582,583,584,585,586,587,588,589,590,591,592,593,594,595,596,597,598,599,600,601,602,603,604,605,606,607,608</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>609,610,611,612,613,614,615,616,617,618,619,620,621,622,623,624,625,626,627,628,629,630,631,632,633,634,635,636,637,638,639,640,641,642,643,644,645,646,647,648,649,650,651,652,653,654,655,656,657,658,659,660,661,662,663,664,665,666,667,668,669,670,671,672,673,674,675,676,677,678,679,680</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>681,682,683,684,685,686,687,688,689,690,691,692,693,694,695,696,697,698,699,700,701,702,703,704,705,706,707,708,709,710,711,712,713,714,715,716,717,718,719,720,721,722,723,724,725,726,727,728,729,730,731,732,733,734,735,736,737,738,739,740,741,742,743,744,745,746,747,748,749,750,751,752,753,754,755,756</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>757,758,759,760,761,762,763,764,765,766,767,768,769,770,771,772,773,774,775,776,777,778,779,780,781,782,783,784,785,786,787,788,789,790,791,792,793,794,795,796,797,798,799,800,801,802,803,804,805,806,807,808,809,810,811,812,813,814,815,816,817,818,819,820,821,822,823,824,825,826,827,828,829,830,831,832,833,834,835,836</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2,3,4,5,6,7,8</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>477,478,479,480,481,482,483,484,485,486,487,488,489,490,491,492,493,494,495,496,497,498,499,500,501,502,503,504,505,506,507,508,509,510,511,512,513,514,515,516,517,518,519,520,521,522,523,524,525,526,527,528,529,530,531,532,533,534,535,536,537,538,539,540</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,7 +219,6 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -249,45 +226,159 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="10"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Consolas"/>
-      <family val="3"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -300,8 +391,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -309,46 +586,325 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -635,14 +1191,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="C3:H24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="3" style="2" customWidth="1"/>
     <col min="2" max="2" width="3.875" style="2" customWidth="1"/>
@@ -654,7 +1210,7 @@
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:8">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -664,64 +1220,64 @@
       <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="3:8">
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8">
+      <c r="C5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="G5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="6" s="1" customFormat="1" spans="3:8">
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="4" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="1">
@@ -730,19 +1286,19 @@
       <c r="G6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H6" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8">
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>17</v>
+      <c r="D7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -750,39 +1306,39 @@
       <c r="G7" s="1">
         <v>2</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H7" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8">
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="5">
+      <c r="D8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="1">
         <v>0</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H8" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8">
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>19</v>
+      <c r="D9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -790,19 +1346,19 @@
       <c r="G9" s="1">
         <v>4</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H9" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8">
       <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>20</v>
+      <c r="D10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -810,39 +1366,39 @@
       <c r="G10" s="1">
         <v>5</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H10" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="3:8">
       <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="5">
+      <c r="D11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
         <v>6</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H11" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="3:8">
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>22</v>
+      <c r="D12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -850,19 +1406,19 @@
       <c r="G12" s="1">
         <v>7</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H12" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="3:8">
       <c r="C13" s="1">
         <v>8</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>23</v>
+      <c r="D13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -870,39 +1426,39 @@
       <c r="G13" s="1">
         <v>8</v>
       </c>
-      <c r="H13" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H13" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="3:8">
       <c r="C14" s="1">
         <v>9</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="5">
+      <c r="D14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1">
         <v>9</v>
       </c>
-      <c r="H14" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H14" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="3:8">
       <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>25</v>
+      <c r="D15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -910,19 +1466,19 @@
       <c r="G15" s="1">
         <v>10</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H15" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="3:8">
       <c r="C16" s="1">
         <v>11</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>26</v>
+      <c r="D16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -930,39 +1486,39 @@
       <c r="G16" s="1">
         <v>11</v>
       </c>
-      <c r="H16" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H16" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="3:8">
       <c r="C17" s="1">
         <v>12</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="5">
+      <c r="D17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1">
         <v>12</v>
       </c>
-      <c r="H17" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H17" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="3:8">
       <c r="C18" s="1">
         <v>13</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>28</v>
+      <c r="D18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -970,19 +1526,19 @@
       <c r="G18" s="1">
         <v>13</v>
       </c>
-      <c r="H18" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H18" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="3:8">
       <c r="C19" s="1">
         <v>14</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>29</v>
+      <c r="D19" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -990,39 +1546,39 @@
       <c r="G19" s="1">
         <v>14</v>
       </c>
-      <c r="H19" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H19" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="3:8">
       <c r="C20" s="1">
         <v>15</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" s="5">
+      <c r="D20" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
         <v>15</v>
       </c>
-      <c r="H20" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H20" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="3:8">
       <c r="C21" s="1">
         <v>16</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>31</v>
+      <c r="D21" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -1030,19 +1586,19 @@
       <c r="G21" s="1">
         <v>16</v>
       </c>
-      <c r="H21" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H21" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="3:8">
       <c r="C22" s="1">
         <v>17</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>32</v>
+      <c r="D22" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -1050,39 +1606,39 @@
       <c r="G22" s="1">
         <v>17</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="7" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:8">
       <c r="C23" s="1">
         <v>18</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F23" s="5">
+      <c r="D23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" s="1">
         <v>0</v>
       </c>
       <c r="G23" s="1">
         <v>18</v>
       </c>
-      <c r="H23" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H23" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="3:8">
       <c r="C24" s="1">
         <v>19</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>34</v>
+      <c r="D24" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -1090,13 +1646,13 @@
       <c r="G24" s="1">
         <v>19</v>
       </c>
-      <c r="H24" s="9" t="s">
-        <v>51</v>
+      <c r="H24" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>